--- a/tokenDemo/close_records.xlsx
+++ b/tokenDemo/close_records.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,60 +414,585 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>平仓时间</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>交易品种</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>持仓方向</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>开仓价格</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>平仓价格</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>平仓数量</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>平仓盈亏(USDT/CNY)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>平仓收益率</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>平仓比例</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>策略标签</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>平仓依据</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>多空比</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>基差率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:30:08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>新农开发 600359</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-44.00000000000004</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-5.75%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>移动止损(轨道)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:30:08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>神奇制药 600613</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="F3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-368.0000000000003</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-15.49%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BZ,DCA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>初始止损</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:30:09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>捷荣技术 002855</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="F4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>128.9999999999999</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8.01%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>首次止盈</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:31:08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>锦龙股份 000712</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="F5" t="n">
+        <v>200</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-164.0000000000001</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-6.56%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>BZ,DCA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>初始止损</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:32:10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>南宁百货 600712</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.81%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BZ,N</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>首次止盈</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:43:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>沃特股份 002886</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="E7" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="F7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-205.9999999999999</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-7.09%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>移动止损(轨道)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:50:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>云赛智联 600602</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="F8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" t="n">
+        <v>41.00000000000001</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.19%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BZ,N</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>首次止盈</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:53:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>华锦股份 000059</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33.99999999999999</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5.92%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>首次止盈</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:56:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>榕基软件 002474</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16.99999999999999</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.67%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>BZ,N</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>首次止盈</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:26:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>诚迈科技 300598</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" t="n">
+        <v>146.0000000000001</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4.32%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>BZ,N</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>首次止盈</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -492,58 +1005,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J557"/>
+  <dimension ref="A1:M560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>平仓时间</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>交易品种</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>持仓方向</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>开仓价格</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>平仓价格</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>平仓数量</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>平仓盈亏(USDT/CNY)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>平仓收益率</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>平仓比例</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>策略标签</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>平仓依据</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>多空比</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>基差率</t>
         </is>
       </c>
     </row>
@@ -590,6 +1118,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -634,6 +1165,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -678,6 +1212,9 @@
           <t>LONG</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -722,6 +1259,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -766,6 +1306,9 @@
           <t>SHORT</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -810,6 +1353,9 @@
           <t>LONG</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -854,6 +1400,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -898,6 +1447,9 @@
           <t>LONG</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -942,6 +1494,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -986,6 +1541,9 @@
           <t>SHORT</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1030,6 +1588,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1074,6 +1635,9 @@
           <t>LONG</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1118,6 +1682,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1162,6 +1729,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1206,6 +1776,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1250,6 +1823,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1294,6 +1870,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1338,6 +1917,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1382,6 +1964,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1426,6 +2011,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1470,6 +2058,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1514,6 +2105,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1558,6 +2152,9 @@
           <t>LONG</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1602,6 +2199,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1646,6 +2246,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1690,6 +2293,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1734,6 +2340,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1778,6 +2387,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1822,6 +2434,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1866,6 +2481,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1910,6 +2528,9 @@
           <t>LONG</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1954,6 +2575,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1998,6 +2622,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2042,6 +2669,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2086,6 +2716,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2130,6 +2763,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2174,6 +2810,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2218,6 +2857,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2262,6 +2904,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2306,6 +2951,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2350,6 +2998,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2394,6 +3045,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2438,6 +3092,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2482,6 +3139,9 @@
           <t>LONG</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2526,6 +3186,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2570,6 +3233,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2614,6 +3280,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2658,6 +3327,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2702,6 +3374,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2746,6 +3421,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2790,6 +3468,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2834,6 +3515,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2878,6 +3562,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2922,6 +3609,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2966,6 +3656,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3010,6 +3703,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3054,6 +3750,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3098,6 +3797,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3142,6 +3844,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3186,6 +3891,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3230,6 +3938,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3274,6 +3985,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3318,6 +4032,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3362,6 +4079,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3406,6 +4126,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3450,6 +4173,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3494,6 +4220,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3538,6 +4267,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3582,6 +4314,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3626,6 +4361,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3670,6 +4408,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3714,6 +4455,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3758,6 +4502,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3802,6 +4549,9 @@
           <t>BD</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3846,6 +4596,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3890,6 +4643,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3934,6 +4690,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3978,6 +4737,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4022,6 +4784,9 @@
           <t>BD</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4066,6 +4831,9 @@
           <t>SHORT</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4110,6 +4878,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4154,6 +4925,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4198,6 +4972,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4242,6 +5019,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4286,6 +5066,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4330,6 +5113,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4374,6 +5160,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4418,6 +5207,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4462,6 +5254,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4506,6 +5301,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4550,6 +5348,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4594,6 +5395,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4638,6 +5442,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4682,6 +5489,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4726,6 +5536,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4770,6 +5583,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4814,6 +5630,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4858,6 +5677,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4902,6 +5724,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4946,6 +5771,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4990,6 +5818,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5034,6 +5865,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5078,6 +5912,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5122,6 +5959,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5166,6 +6006,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5210,6 +6053,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5254,6 +6100,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5298,6 +6147,9 @@
           <t>SHORT</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5342,6 +6194,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5386,6 +6241,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5430,6 +6288,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5474,6 +6335,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5518,6 +6382,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5562,6 +6429,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5606,6 +6476,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5650,6 +6523,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5694,6 +6570,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5738,6 +6617,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5782,6 +6664,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5826,6 +6711,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5870,6 +6758,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5914,6 +6805,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5958,6 +6852,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6002,6 +6899,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6046,6 +6946,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6090,6 +6993,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6134,6 +7040,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6178,6 +7087,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6222,6 +7134,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6266,6 +7181,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6310,6 +7228,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6354,6 +7275,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6398,6 +7322,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6442,6 +7369,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6486,6 +7416,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6530,6 +7463,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6574,6 +7510,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6618,6 +7557,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6662,6 +7604,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6706,6 +7651,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6750,6 +7698,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6794,6 +7745,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6838,6 +7792,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6882,6 +7839,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6926,6 +7886,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6970,6 +7933,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7014,6 +7980,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7058,6 +8027,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7102,6 +8074,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7146,6 +8121,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7190,6 +8168,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7234,6 +8215,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7278,6 +8262,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7322,6 +8309,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7366,6 +8356,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7410,6 +8403,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7454,6 +8450,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7498,6 +8497,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7542,6 +8544,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7586,6 +8591,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7630,6 +8638,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7674,6 +8685,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7718,6 +8732,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7762,6 +8779,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7806,6 +8826,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7850,6 +8873,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7894,6 +8920,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7938,6 +8967,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7982,6 +9014,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8026,6 +9061,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8070,6 +9108,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8114,6 +9155,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8158,6 +9202,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8202,6 +9249,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8246,6 +9296,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8290,6 +9343,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8334,6 +9390,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8378,6 +9437,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8422,6 +9484,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8466,6 +9531,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8510,6 +9578,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8554,6 +9625,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8598,6 +9672,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8642,6 +9719,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8686,6 +9766,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8730,6 +9813,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8774,6 +9860,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8818,6 +9907,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8862,6 +9954,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8906,6 +10001,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8950,6 +10048,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8994,6 +10095,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9038,6 +10142,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9082,6 +10189,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9126,6 +10236,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9170,6 +10283,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9214,6 +10330,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9258,6 +10377,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9302,6 +10424,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9346,6 +10471,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9390,6 +10518,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9434,6 +10565,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9478,6 +10612,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9522,6 +10659,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9566,6 +10706,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9610,6 +10753,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9654,6 +10800,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9698,6 +10847,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9742,6 +10894,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9786,6 +10941,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9830,6 +10988,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9874,6 +11035,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9918,6 +11082,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9962,6 +11129,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10006,6 +11176,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10050,6 +11223,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10094,6 +11270,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10138,6 +11317,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10182,6 +11364,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10226,6 +11411,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10270,6 +11458,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10314,6 +11505,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10358,6 +11552,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10402,6 +11599,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10446,6 +11646,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10490,6 +11693,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10534,6 +11740,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10578,6 +11787,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10622,6 +11834,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10666,6 +11881,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10710,6 +11928,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10754,6 +11975,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10798,6 +12022,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10842,6 +12069,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10886,6 +12116,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10930,6 +12163,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10974,6 +12210,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11018,6 +12257,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11062,6 +12304,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11106,6 +12351,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11150,6 +12398,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11194,6 +12445,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11238,6 +12492,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11282,6 +12539,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11326,6 +12586,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11370,6 +12633,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11414,6 +12680,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11458,6 +12727,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11502,6 +12774,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11546,6 +12821,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -11590,6 +12868,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -11634,6 +12915,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -11678,6 +12962,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -11722,6 +13009,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -11766,6 +13056,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -11810,6 +13103,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -11854,6 +13150,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -11898,6 +13197,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -11942,6 +13244,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -11986,6 +13291,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12030,6 +13338,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12074,6 +13385,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12118,6 +13432,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12162,6 +13479,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12206,6 +13526,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12250,6 +13573,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -12294,6 +13620,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -12338,6 +13667,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12382,6 +13714,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12426,6 +13761,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -12470,6 +13808,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -12514,6 +13855,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -12558,6 +13902,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -12602,6 +13949,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -12646,6 +13996,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -12690,6 +14043,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -12734,6 +14090,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -12778,6 +14137,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -12822,6 +14184,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -12866,6 +14231,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -12910,6 +14278,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -12954,6 +14325,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -12998,6 +14372,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13042,6 +14419,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -13086,6 +14466,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -13130,6 +14513,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -13174,6 +14560,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -13218,6 +14607,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -13262,6 +14654,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -13306,6 +14701,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -13350,6 +14748,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -13394,6 +14795,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -13438,6 +14842,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -13482,6 +14889,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -13526,6 +14936,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -13570,6 +14983,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -13614,6 +15030,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -13658,6 +15077,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -13702,6 +15124,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -13746,6 +15171,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -13790,6 +15218,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -13834,6 +15265,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -13878,6 +15312,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -13922,6 +15359,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -13966,6 +15406,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14010,6 +15453,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14054,6 +15500,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14098,6 +15547,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14142,6 +15594,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14186,6 +15641,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -14230,6 +15688,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -14274,6 +15735,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -14318,6 +15782,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14362,6 +15829,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -14406,6 +15876,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -14450,6 +15923,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -14494,6 +15970,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -14538,6 +16017,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -14582,6 +16064,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -14626,6 +16111,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -14670,6 +16158,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -14714,6 +16205,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -14758,6 +16252,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -14802,6 +16299,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -14846,6 +16346,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -14890,6 +16393,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -14934,6 +16440,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -14978,6 +16487,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15022,6 +16534,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15066,6 +16581,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -15110,6 +16628,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -15154,6 +16675,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -15198,6 +16722,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15242,6 +16769,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -15286,6 +16816,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15330,6 +16863,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -15374,6 +16910,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -15418,6 +16957,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -15462,6 +17004,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -15506,6 +17051,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -15550,6 +17098,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -15594,6 +17145,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -15638,6 +17192,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -15682,6 +17239,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -15726,6 +17286,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -15770,6 +17333,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -15814,6 +17380,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -15858,6 +17427,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -15902,6 +17474,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -15946,6 +17521,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -15990,6 +17568,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -16034,6 +17615,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -16078,6 +17662,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -16122,6 +17709,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -16166,6 +17756,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -16210,6 +17803,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -16254,6 +17850,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -16298,6 +17897,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -16342,6 +17944,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -16386,6 +17991,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -16430,6 +18038,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -16474,6 +18085,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -16518,6 +18132,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -16562,6 +18179,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -16606,6 +18226,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -16650,6 +18273,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -16694,6 +18320,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -16738,6 +18367,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -16782,6 +18414,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -16826,6 +18461,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -16870,6 +18508,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -16914,6 +18555,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -16958,6 +18602,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -17002,6 +18649,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -17046,6 +18696,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -17090,6 +18743,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -17134,6 +18790,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -17178,6 +18837,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -17222,6 +18884,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -17266,6 +18931,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -17310,6 +18978,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -17354,6 +19025,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -17398,6 +19072,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -17442,6 +19119,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -17486,6 +19166,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -17530,6 +19213,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -17574,6 +19260,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -17618,6 +19307,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -17662,6 +19354,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -17706,6 +19401,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -17750,6 +19448,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -17794,6 +19495,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -17838,6 +19542,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -17882,6 +19589,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -17926,6 +19636,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -17970,6 +19683,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -18014,6 +19730,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -18058,6 +19777,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -18102,6 +19824,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -18146,6 +19871,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -18190,6 +19918,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -18234,6 +19965,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -18278,6 +20012,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -18322,6 +20059,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -18366,6 +20106,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -18410,6 +20153,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -18454,6 +20200,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -18498,6 +20247,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -18542,6 +20294,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -18586,6 +20341,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -18630,6 +20388,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -18674,6 +20435,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -18718,6 +20482,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -18762,6 +20529,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -18806,6 +20576,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -18850,6 +20623,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -18894,6 +20670,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -18938,6 +20717,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -18982,6 +20764,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -19026,6 +20811,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -19070,6 +20858,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -19114,6 +20905,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -19158,6 +20952,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -19202,6 +20999,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -19246,6 +21046,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -19290,6 +21093,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -19334,6 +21140,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -19378,6 +21187,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -19422,6 +21234,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -19466,6 +21281,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -19510,6 +21328,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -19554,6 +21375,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -19598,6 +21422,9 @@
           <t>BZ</t>
         </is>
       </c>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -19642,6 +21469,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -19686,6 +21516,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -19730,6 +21563,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -19774,6 +21610,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -19818,6 +21657,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -19862,6 +21704,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K440" t="inlineStr"/>
+      <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -19906,6 +21751,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -19950,6 +21798,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -19994,6 +21845,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -20038,6 +21892,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -20082,6 +21939,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -20126,6 +21986,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -20170,6 +22033,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -20214,6 +22080,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -20258,6 +22127,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -20302,6 +22174,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -20346,6 +22221,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K451" t="inlineStr"/>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -20390,6 +22268,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K452" t="inlineStr"/>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -20434,6 +22315,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -20478,6 +22362,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -20522,6 +22409,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -20566,6 +22456,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -20610,6 +22503,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -20654,6 +22550,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -20698,6 +22597,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -20742,6 +22644,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -20786,6 +22691,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -20830,6 +22738,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -20874,6 +22785,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -20918,6 +22832,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -20962,6 +22879,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -21006,6 +22926,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -21050,6 +22973,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -21094,6 +23020,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K468" t="inlineStr"/>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -21138,6 +23067,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K469" t="inlineStr"/>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -21182,6 +23114,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -21226,6 +23161,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K471" t="inlineStr"/>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -21270,6 +23208,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -21314,6 +23255,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -21358,6 +23302,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -21402,6 +23349,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -21446,6 +23396,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -21490,6 +23443,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -21534,6 +23490,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -21578,6 +23537,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -21622,6 +23584,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -21666,6 +23631,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -21710,6 +23678,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -21754,6 +23725,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -21798,6 +23772,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -21842,6 +23819,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -21886,6 +23866,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -21930,6 +23913,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -21974,6 +23960,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -22018,6 +24007,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -22062,6 +24054,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -22106,6 +24101,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -22150,6 +24148,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -22194,6 +24195,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -22238,6 +24242,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -22282,6 +24289,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -22326,6 +24336,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -22370,6 +24383,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -22414,6 +24430,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -22458,6 +24477,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -22502,6 +24524,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -22546,6 +24571,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -22590,6 +24618,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -22634,6 +24665,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -22678,6 +24712,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -22722,6 +24759,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -22766,6 +24806,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -22810,6 +24853,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -22854,6 +24900,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -22898,6 +24947,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -22942,6 +24994,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -22986,6 +25041,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -23030,6 +25088,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -23074,6 +25135,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -23118,6 +25182,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -23162,6 +25229,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -23206,6 +25276,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -23250,6 +25323,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -23294,6 +25370,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -23338,6 +25417,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -23382,6 +25464,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -23426,6 +25511,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -23470,6 +25558,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -23514,6 +25605,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -23558,6 +25652,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -23602,6 +25699,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -23646,6 +25746,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -23690,6 +25793,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -23734,6 +25840,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -23778,6 +25887,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -23822,6 +25934,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -23866,6 +25981,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -23910,6 +26028,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -23954,6 +26075,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -23998,6 +26122,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -24042,6 +26169,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -24086,6 +26216,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -24130,6 +26263,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -24174,6 +26310,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -24218,6 +26357,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -24262,6 +26404,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -24306,6 +26451,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -24350,6 +26498,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -24394,6 +26545,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -24438,6 +26592,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -24482,6 +26639,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -24526,6 +26686,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -24570,6 +26733,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -24614,6 +26780,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -24658,6 +26827,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -24702,6 +26874,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -24746,6 +26921,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -24790,6 +26968,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -24834,6 +27015,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -24878,6 +27062,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -24922,6 +27109,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr"/>
+      <c r="M555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -24966,6 +27156,9 @@
           <t>Supertrend</t>
         </is>
       </c>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr"/>
+      <c r="M556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -25008,6 +27201,180 @@
       <c r="J557" t="inlineStr">
         <is>
           <t>Supertrend</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr"/>
+      <c r="L557" t="inlineStr"/>
+      <c r="M557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-31 19:30:04</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>AXLUSDT</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>0.05013159480364934</v>
+      </c>
+      <c r="E558" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="F558" t="n">
+        <v>3529.3</v>
+      </c>
+      <c r="G558" t="n">
+        <v>10.12346245948037</v>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>5.72%</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>70.00%</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>首次止盈</t>
+        </is>
+      </c>
+      <c r="L558" t="n">
+        <v>1.4938</v>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>-0.5797%</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-31 19:31:03</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>AXLUSDT</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>0.05013159480364934</v>
+      </c>
+      <c r="E559" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="F559" t="n">
+        <v>1512.7</v>
+      </c>
+      <c r="G559" t="n">
+        <v>0.935461540519644</v>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>首次止盈</t>
+        </is>
+      </c>
+      <c r="L559" t="n">
+        <v>1.4938</v>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>-0.5797%</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-08-31 20:58:03</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>SKRUSDT</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>0.02687525300950369</v>
+      </c>
+      <c r="E560" t="n">
+        <v>0.025012</v>
+      </c>
+      <c r="F560" t="n">
+        <v>9470</v>
+      </c>
+      <c r="G560" t="n">
+        <v>-17.645006</v>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-6.93%</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>BZ,Basis</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>初始止损</t>
+        </is>
+      </c>
+      <c r="L560" t="n">
+        <v>0.7976</v>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>-5.1964%</t>
         </is>
       </c>
     </row>

--- a/tokenDemo/close_records.xlsx
+++ b/tokenDemo/close_records.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,6 +993,57 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:37:02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>潞化科技 600691</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12.00000000000001</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3.72%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>首次止盈</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1005,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M560"/>
+  <dimension ref="A1:M561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27378,6 +27429,65 @@
         </is>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:03:02</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>AGTUSDT</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>0.01762783449924071</v>
+      </c>
+      <c r="E561" t="n">
+        <v>0.015668</v>
+      </c>
+      <c r="F561" t="n">
+        <v>40169</v>
+      </c>
+      <c r="G561" t="n">
+        <v>-78.72459199999987</v>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-11.12%</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>BZ,DCA*2</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>移动止损(轨道)</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>1.5458</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>0.2979%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
